--- a/【pip】上证指数旗形运行结果/不同order结果/pattern_performance_summary.xlsx
+++ b/【pip】上证指数旗形运行结果/不同order结果/pattern_performance_summary.xlsx
@@ -16,52 +16,52 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
-    <t>牛市旗形数量</t>
+    <t>bull_flag_count</t>
   </si>
   <si>
-    <t>牛市旗形平均对数收益率</t>
+    <t>bull_flag_avg</t>
   </si>
   <si>
-    <t>牛市旗形胜率</t>
+    <t>bull_flag_wr</t>
   </si>
   <si>
-    <t>牛市旗形总收益</t>
+    <t>bull_flag_total</t>
   </si>
   <si>
-    <t>熊旗数量</t>
+    <t>bear_flag_count</t>
   </si>
   <si>
-    <t>熊旗平均对数收益率</t>
+    <t>bear_flag_avg</t>
   </si>
   <si>
-    <t>熊旗胜率</t>
+    <t>bear_flag_wr</t>
   </si>
   <si>
-    <t>熊旗总收益</t>
+    <t>bear_flag_total</t>
   </si>
   <si>
-    <t>牛市三角旗数量</t>
+    <t>bull_pennant_count</t>
   </si>
   <si>
-    <t>牛市三角旗平均对数收益率</t>
+    <t>bull_pennant_avg</t>
   </si>
   <si>
-    <t>牛市三角旗胜率</t>
+    <t>bull_pennant_wr</t>
   </si>
   <si>
-    <t>牛市三角旗总收益</t>
+    <t>bull_pennant_total</t>
   </si>
   <si>
-    <t>熊市三角旗数量</t>
+    <t>bear_pennant_count</t>
   </si>
   <si>
-    <t>熊市三角旗平均对数收益率</t>
+    <t>bear_pennant_avg</t>
   </si>
   <si>
-    <t>熊市三角旗胜率</t>
+    <t>bear_pennant_wr</t>
   </si>
   <si>
-    <t>熊市三角旗总收益</t>
+    <t>bear_pennant_total</t>
   </si>
 </sst>
 </file>
@@ -419,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -474,31 +474,31 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0.06102723872871874</v>
+        <v>0.03165084965586296</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>0.1220544774574375</v>
+        <v>0.03165084965586296</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>0.02065325676376695</v>
+        <v>0.04334470844900817</v>
       </c>
       <c r="H2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0.04130651352753389</v>
+        <v>0.08668941689801635</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -515,37 +515,43 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.06102723872871874</v>
+        <v>0.03165084965586296</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>0.1220544774574375</v>
+        <v>0.03165084965586296</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>-0.002250124575467138</v>
+        <v>0.0499474683559562</v>
       </c>
       <c r="H3">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>-0.009000498301868554</v>
+        <v>0.1498424050678686</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>0.02569349612903338</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>0.02569349612903338</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -556,1197 +562,1179 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>0.04154746015730856</v>
+        <v>0.005946516297527182</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E4">
-        <v>0.1246423804719257</v>
+        <v>0.01189303259505436</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>-8.641185623581293E-05</v>
+        <v>0.02833137036895961</v>
       </c>
       <c r="H4">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="I4">
-        <v>-0.0006912948498865035</v>
+        <v>0.1133254814758384</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="K4">
-        <v>-0.0191882107826844</v>
+        <v>0.02569349612903338</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>-0.0191882107826844</v>
+        <v>0.02569349612903338</v>
       </c>
       <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>0.01227302384298223</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>0.01227302384298223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>0.01308918450599046</v>
+        <v>0.01175324512526318</v>
       </c>
       <c r="D5">
-        <v>0.7142857142857143</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E5">
-        <v>0.09162429154193319</v>
+        <v>0.03525973537578952</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>0.02216079957600705</v>
+        <v>0.01440542585625337</v>
       </c>
       <c r="H5">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I5">
-        <v>0.2216079957600705</v>
+        <v>0.07202712928126687</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0.004507637077376299</v>
+        <v>0.02569349612903338</v>
       </c>
       <c r="L5">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>0.0135229112321289</v>
+        <v>0.02569349612903338</v>
       </c>
       <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>0.01227302384298223</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>0.01227302384298223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>0.002947177980215023</v>
+        <v>-0.02004328951885039</v>
       </c>
       <c r="D6">
-        <v>0.6363636363636364</v>
+        <v>0.4</v>
       </c>
       <c r="E6">
-        <v>0.03241895778236525</v>
+        <v>-0.100216447594252</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>0.01895267036831844</v>
+        <v>0.0262331478122723</v>
       </c>
       <c r="H6">
-        <v>0.5384615384615384</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I6">
-        <v>0.2463847147881397</v>
+        <v>0.1573988868736338</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0.007744975290630007</v>
+        <v>0.02569349612903338</v>
       </c>
       <c r="L6">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>0.03097990116252003</v>
+        <v>0.02569349612903338</v>
       </c>
       <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>0.01227302384298223</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.01227302384298223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>0.003792858406555411</v>
+        <v>-0.02097474328645355</v>
       </c>
       <c r="D7">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E7">
-        <v>0.05310001769177575</v>
+        <v>-0.1468232030051748</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>0.01464902589954058</v>
+        <v>0.01507390083490259</v>
       </c>
       <c r="H7">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I7">
-        <v>0.2050863625935682</v>
+        <v>0.1356651075141233</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0.004038363890138541</v>
+        <v>0.02569349612903338</v>
       </c>
       <c r="L7">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>0.02019181945069271</v>
+        <v>0.02569349612903338</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7">
-        <v>0.009020070922676648</v>
+        <v>0.005155551863698093</v>
       </c>
       <c r="P7">
         <v>1</v>
       </c>
       <c r="Q7">
-        <v>0.0180401418453533</v>
+        <v>0.005155551863698093</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="1">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>-0.0297456754435063</v>
+      </c>
+      <c r="D8">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="E8">
+        <v>-0.1784740526610378</v>
+      </c>
+      <c r="F8">
         <v>9</v>
       </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>-0.00167445484824853</v>
-      </c>
-      <c r="D8">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="E8">
-        <v>-0.02511682272372795</v>
-      </c>
-      <c r="F8">
-        <v>16</v>
-      </c>
       <c r="G8">
-        <v>0.01447596934432249</v>
+        <v>0.01941224187161299</v>
       </c>
       <c r="H8">
-        <v>0.5625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I8">
-        <v>0.2316155095091599</v>
+        <v>0.174710176844517</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>0.004038363890138541</v>
+        <v>-0.007619992228861783</v>
       </c>
       <c r="L8">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M8">
-        <v>0.02019181945069271</v>
+        <v>-0.01523998445772357</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8">
-        <v>0.009020070922676648</v>
+        <v>0.005155551863698093</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="Q8">
-        <v>0.0180401418453533</v>
+        <v>0.005155551863698093</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>-0.00293386615926133</v>
+        <v>-0.02321889920730261</v>
       </c>
       <c r="D9">
-        <v>0.4705882352941176</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E9">
-        <v>-0.04987572470744261</v>
+        <v>-0.1625322944511183</v>
       </c>
       <c r="F9">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>0.01010374218710187</v>
+        <v>0.01941224187161299</v>
       </c>
       <c r="H9">
-        <v>0.5555555555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I9">
-        <v>0.1818673593678337</v>
+        <v>0.174710176844517</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>0.004038363890138541</v>
+        <v>-0.007619992228861783</v>
       </c>
       <c r="L9">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M9">
-        <v>0.02019181945069271</v>
+        <v>-0.01523998445772357</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9">
-        <v>0.00773189790301713</v>
+        <v>0.01791131788630507</v>
       </c>
       <c r="P9">
         <v>1</v>
       </c>
       <c r="Q9">
-        <v>0.02319569370905139</v>
+        <v>0.03582263577261013</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>-0.006588350022406764</v>
+        <v>-0.02321889920730261</v>
       </c>
       <c r="D10">
-        <v>0.4375</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E10">
-        <v>-0.1054136003585082</v>
+        <v>-0.1625322944511183</v>
       </c>
       <c r="F10">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>0.02579728254724737</v>
+        <v>0.02475782717756905</v>
       </c>
       <c r="H10">
         <v>0.6666666666666666</v>
       </c>
       <c r="I10">
-        <v>0.4643510858504527</v>
+        <v>0.2228204445981214</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K10">
-        <v>-0.001015645833878143</v>
+        <v>-0.007619992228861783</v>
       </c>
       <c r="L10">
         <v>0.5</v>
       </c>
       <c r="M10">
-        <v>-0.006093875003268856</v>
+        <v>-0.01523998445772357</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10">
-        <v>0.00773189790301713</v>
+        <v>0.01791131788630507</v>
       </c>
       <c r="P10">
         <v>1</v>
       </c>
       <c r="Q10">
-        <v>0.02319569370905139</v>
+        <v>0.03582263577261013</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>-0.005263049538152278</v>
+        <v>-0.0161784959574406</v>
       </c>
       <c r="D11">
-        <v>0.4705882352941176</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="E11">
-        <v>-0.08947184214858872</v>
+        <v>-0.1132494717020842</v>
       </c>
       <c r="F11">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>0.02419913902114311</v>
+        <v>0.02475782717756905</v>
       </c>
       <c r="H11">
-        <v>0.631578947368421</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I11">
-        <v>0.4597836414017191</v>
+        <v>0.2228204445981214</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K11">
-        <v>-0.001015645833878143</v>
+        <v>-0.007619992228861783</v>
       </c>
       <c r="L11">
         <v>0.5</v>
       </c>
       <c r="M11">
-        <v>-0.006093875003268856</v>
+        <v>-0.01523998445772357</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>0.02257823230282282</v>
+        <v>0.01791131788630507</v>
       </c>
       <c r="P11">
         <v>1</v>
       </c>
       <c r="Q11">
-        <v>0.1354693938169369</v>
+        <v>0.03582263577261013</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>-0.003458756680180586</v>
+        <v>-0.02008161219744942</v>
       </c>
       <c r="D12">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="E12">
-        <v>-0.05534010688288937</v>
+        <v>-0.1606528975795953</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>0.02345250092296829</v>
+        <v>0.01350658426363833</v>
       </c>
       <c r="H12">
-        <v>0.6111111111111112</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I12">
-        <v>0.4221450166134293</v>
+        <v>0.1215592583727449</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K12">
-        <v>-0.0005808547943053632</v>
+        <v>-0.007869661852279108</v>
       </c>
       <c r="L12">
         <v>0.5</v>
       </c>
       <c r="M12">
-        <v>-0.002323419177221453</v>
+        <v>-0.01573932370455822</v>
       </c>
       <c r="N12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O12">
-        <v>0.02257823230282282</v>
+        <v>0.01791131788630507</v>
       </c>
       <c r="P12">
         <v>1</v>
       </c>
       <c r="Q12">
-        <v>0.1354693938169369</v>
+        <v>0.03582263577261013</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>-0.0001843598822385448</v>
+        <v>-0.02008161219744942</v>
       </c>
       <c r="D13">
-        <v>0.5263157894736842</v>
+        <v>0.375</v>
       </c>
       <c r="E13">
-        <v>-0.003502837762532351</v>
+        <v>-0.1606528975795953</v>
       </c>
       <c r="F13">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>0.02345250092296829</v>
+        <v>0.01030831016442431</v>
       </c>
       <c r="H13">
-        <v>0.6111111111111112</v>
+        <v>0.6</v>
       </c>
       <c r="I13">
-        <v>0.4221450166134293</v>
+        <v>0.1030831016442431</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>-0.0005808547943053632</v>
+        <v>-0.007869661852279108</v>
       </c>
       <c r="L13">
         <v>0.5</v>
       </c>
       <c r="M13">
-        <v>-0.002323419177221453</v>
+        <v>-0.01573932370455822</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O13">
-        <v>0.02257823230282282</v>
+        <v>0.01791131788630507</v>
       </c>
       <c r="P13">
         <v>1</v>
       </c>
       <c r="Q13">
-        <v>0.1354693938169369</v>
+        <v>0.03582263577261013</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>-0.003395748899017479</v>
+        <v>-0.02376737396231254</v>
       </c>
       <c r="D14">
-        <v>0.5555555555555556</v>
+        <v>0.25</v>
       </c>
       <c r="E14">
-        <v>-0.06112348018231462</v>
+        <v>-0.1901389916985003</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G14">
-        <v>0.01979129284368242</v>
+        <v>0.002471579499575216</v>
       </c>
       <c r="H14">
-        <v>0.6875</v>
+        <v>0.5</v>
       </c>
       <c r="I14">
-        <v>0.3166606854989187</v>
+        <v>0.01977263599660173</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>-0.006759916118149079</v>
+        <v>-0.04093348058675694</v>
       </c>
       <c r="L14">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>-0.02027974835444724</v>
+        <v>-0.04093348058675694</v>
       </c>
       <c r="N14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O14">
-        <v>0.04012123774469245</v>
+        <v>0.01791131788630507</v>
       </c>
       <c r="P14">
         <v>1</v>
       </c>
       <c r="Q14">
-        <v>0.2407274264681547</v>
+        <v>0.03582263577261013</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B15">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>-0.003395748899017479</v>
+        <v>-0.02376737396231254</v>
       </c>
       <c r="D15">
-        <v>0.5555555555555556</v>
+        <v>0.25</v>
       </c>
       <c r="E15">
-        <v>-0.06112348018231462</v>
+        <v>-0.1901389916985003</v>
       </c>
       <c r="F15">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G15">
-        <v>0.02009297384347498</v>
+        <v>0.002471579499575216</v>
       </c>
       <c r="H15">
-        <v>0.7058823529411765</v>
+        <v>0.5</v>
       </c>
       <c r="I15">
-        <v>0.3415805553390747</v>
+        <v>0.01977263599660173</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>-0.006759916118149079</v>
+        <v>-0.04093348058675694</v>
       </c>
       <c r="L15">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>-0.02027974835444724</v>
+        <v>-0.04093348058675694</v>
       </c>
       <c r="N15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O15">
-        <v>0.03014916679066662</v>
+        <v>0.01791131788630507</v>
       </c>
       <c r="P15">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="Q15">
-        <v>0.2110441675346664</v>
+        <v>0.03582263577261013</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B16">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C16">
-        <v>-0.01151276634548879</v>
+        <v>0.002575632394804295</v>
       </c>
       <c r="D16">
         <v>0.4444444444444444</v>
       </c>
       <c r="E16">
-        <v>-0.2072297942187982</v>
+        <v>0.02318069155323865</v>
       </c>
       <c r="F16">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G16">
-        <v>0.02172189893325432</v>
+        <v>0.008613320449874047</v>
       </c>
       <c r="H16">
-        <v>0.7333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I16">
-        <v>0.3258284839988148</v>
+        <v>0.06029324314911833</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>-0.02273695261832298</v>
+        <v>-0.04093348058675694</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>-0.04547390523664596</v>
+        <v>-0.04093348058675694</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O16">
-        <v>0.03047940719727871</v>
+        <v>0.01791131788630507</v>
       </c>
       <c r="P16">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="Q16">
-        <v>0.1828764431836722</v>
+        <v>0.03582263577261013</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B17">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>-0.01151276634548879</v>
+        <v>0.004216049581062768</v>
       </c>
       <c r="D17">
-        <v>0.4444444444444444</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="E17">
-        <v>-0.2072297942187982</v>
+        <v>0.04637654539169045</v>
       </c>
       <c r="F17">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>0.02172189893325432</v>
+        <v>0.008613320449874047</v>
       </c>
       <c r="H17">
-        <v>0.7333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I17">
-        <v>0.3258284839988148</v>
+        <v>0.06029324314911833</v>
       </c>
       <c r="J17">
         <v>2</v>
       </c>
       <c r="K17">
-        <v>-0.02273695261832298</v>
+        <v>0.1157852465798079</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M17">
-        <v>-0.04547390523664596</v>
+        <v>0.2315704931596159</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O17">
-        <v>0.03047940719727871</v>
+        <v>-0.01499356795624696</v>
       </c>
       <c r="P17">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q17">
-        <v>0.1828764431836722</v>
+        <v>-0.04498070386874087</v>
       </c>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B18">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>0.0001506593908026469</v>
+        <v>-0.003953078448801506</v>
       </c>
       <c r="D18">
-        <v>0.5555555555555556</v>
+        <v>0.4</v>
       </c>
       <c r="E18">
-        <v>0.002711869034447645</v>
+        <v>-0.03953078448801506</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>0.03131999629406224</v>
+        <v>0.01613502779019142</v>
       </c>
       <c r="H18">
-        <v>0.7692307692307693</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I18">
-        <v>0.4071599518228091</v>
+        <v>0.09681016674114851</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K18">
-        <v>-0.02628569445396156</v>
+        <v>0.08701518803041471</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M18">
-        <v>-0.02628569445396156</v>
+        <v>0.2610455640912441</v>
       </c>
       <c r="N18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O18">
-        <v>0.006988690756248861</v>
+        <v>-0.01499356795624696</v>
       </c>
       <c r="P18">
         <v>0.6666666666666666</v>
       </c>
       <c r="Q18">
-        <v>0.04193214453749317</v>
+        <v>-0.04498070386874087</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B19">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C19">
-        <v>-0.0001986119451497647</v>
+        <v>-0.003953078448801506</v>
       </c>
       <c r="D19">
-        <v>0.5714285714285714</v>
+        <v>0.4</v>
       </c>
       <c r="E19">
-        <v>-0.004170850848145058</v>
+        <v>-0.03953078448801506</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>0.02689062841666421</v>
+        <v>0.01613502779019142</v>
       </c>
       <c r="H19">
-        <v>0.7142857142857143</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I19">
-        <v>0.376468797833299</v>
+        <v>0.09681016674114851</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19">
-        <v>-0.02628569445396156</v>
+        <v>0.08701518803041471</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M19">
-        <v>-0.02628569445396156</v>
+        <v>0.2610455640912441</v>
       </c>
       <c r="N19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>-0.005553027871979691</v>
+        <v>-0.01499356795624696</v>
       </c>
       <c r="P19">
-        <v>0.5714285714285714</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q19">
-        <v>-0.03887119510385784</v>
+        <v>-0.04498070386874087</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B20">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>-0.00638921516212454</v>
+        <v>-0.00542308006369554</v>
       </c>
       <c r="D20">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="E20">
-        <v>-0.1277843032424908</v>
+        <v>-0.0542308006369554</v>
       </c>
       <c r="F20">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>0.0271526930647222</v>
+        <v>0.001365820449229815</v>
       </c>
       <c r="H20">
-        <v>0.7272727272727273</v>
+        <v>0.6</v>
       </c>
       <c r="I20">
-        <v>0.2986796237119442</v>
+        <v>0.006829102246149077</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>0.001594688238833353</v>
+        <v>0.08701518803041471</v>
       </c>
       <c r="L20">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M20">
-        <v>0.003189376477666706</v>
+        <v>0.2610455640912441</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O20">
-        <v>-0.00743971885103815</v>
+        <v>-0.01499356795624696</v>
       </c>
       <c r="P20">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q20">
-        <v>-0.0446383131062289</v>
+        <v>-0.04498070386874087</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B21">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C21">
-        <v>-0.00638921516212454</v>
+        <v>0.0161373824103364</v>
       </c>
       <c r="D21">
-        <v>0.45</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="E21">
-        <v>-0.1277843032424908</v>
+        <v>0.1775112065137003</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>0.0271526930647222</v>
+        <v>0.0002640846781883551</v>
       </c>
       <c r="H21">
-        <v>0.7272727272727273</v>
+        <v>0.5</v>
       </c>
       <c r="I21">
-        <v>0.2986796237119442</v>
+        <v>0.001584508069130131</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>0.001594688238833353</v>
+        <v>0.08701518803041471</v>
       </c>
       <c r="L21">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M21">
-        <v>0.003189376477666706</v>
+        <v>0.2610455640912441</v>
       </c>
       <c r="N21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O21">
-        <v>-0.00743971885103815</v>
+        <v>-0.01499356795624696</v>
       </c>
       <c r="P21">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q21">
-        <v>-0.0446383131062289</v>
+        <v>-0.04498070386874087</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B22">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C22">
-        <v>-0.003530813626797368</v>
+        <v>0.03034334638014939</v>
       </c>
       <c r="D22">
-        <v>0.4117647058823529</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E22">
-        <v>-0.06002383165555525</v>
+        <v>0.2730901174213445</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G22">
-        <v>0.01815999317322239</v>
+        <v>0.0002640846781883551</v>
       </c>
       <c r="H22">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="I22">
-        <v>0.1634399385590015</v>
+        <v>0.001584508069130131</v>
       </c>
       <c r="J22">
         <v>3</v>
       </c>
       <c r="K22">
-        <v>0.0838554870558843</v>
+        <v>0.08701518803041471</v>
       </c>
       <c r="L22">
         <v>0.6666666666666666</v>
       </c>
       <c r="M22">
-        <v>0.2515664611676529</v>
+        <v>0.2610455640912441</v>
       </c>
       <c r="N22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O22">
-        <v>-0.02752217996593728</v>
+        <v>-0.01499356795624696</v>
       </c>
       <c r="P22">
-        <v>0.4285714285714285</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q22">
-        <v>-0.1926552597615609</v>
+        <v>-0.04498070386874087</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B23">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C23">
-        <v>0.009539898638616694</v>
+        <v>0.03544683613249892</v>
       </c>
       <c r="D23">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="E23">
-        <v>0.1717181754951005</v>
+        <v>0.3544683613249893</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>0.01815999317322239</v>
+        <v>0.0002640846781883551</v>
       </c>
       <c r="H23">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="I23">
-        <v>0.1634399385590015</v>
+        <v>0.001584508069130131</v>
       </c>
       <c r="J23">
         <v>3</v>
       </c>
       <c r="K23">
-        <v>0.0838554870558843</v>
+        <v>0.08701518803041471</v>
       </c>
       <c r="L23">
         <v>0.6666666666666666</v>
       </c>
       <c r="M23">
-        <v>0.2515664611676529</v>
+        <v>0.2610455640912441</v>
       </c>
       <c r="N23">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O23">
-        <v>-0.02758236617068222</v>
+        <v>-0.01499356795624696</v>
       </c>
       <c r="P23">
-        <v>0.375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q23">
-        <v>-0.2206589293654577</v>
+        <v>-0.04498070386874087</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B24">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C24">
-        <v>0.007655442772088683</v>
+        <v>0.03435954128337446</v>
       </c>
       <c r="D24">
-        <v>0.3125</v>
+        <v>0.5</v>
       </c>
       <c r="E24">
-        <v>0.1224870843534189</v>
+        <v>0.3435954128337446</v>
       </c>
       <c r="F24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G24">
-        <v>0.01368712293014992</v>
+        <v>-0.00954937259725345</v>
       </c>
       <c r="H24">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I24">
-        <v>0.1231841063713492</v>
+        <v>-0.0572962355835207</v>
       </c>
       <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <v>0.1509895223390005</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>0.3019790446780011</v>
+      </c>
+      <c r="N24">
         <v>3</v>
       </c>
-      <c r="K24">
-        <v>0.08701518803041471</v>
-      </c>
-      <c r="L24">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="M24">
-        <v>0.2610455640912441</v>
-      </c>
-      <c r="N24">
-        <v>8</v>
-      </c>
       <c r="O24">
-        <v>-0.02758236617068222</v>
+        <v>-0.01499356795624696</v>
       </c>
       <c r="P24">
-        <v>0.375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q24">
-        <v>-0.2206589293654577</v>
+        <v>-0.04498070386874087</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B25">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>0.01156954346239993</v>
+        <v>0.03435954128337446</v>
       </c>
       <c r="D25">
-        <v>0.3529411764705883</v>
+        <v>0.5</v>
       </c>
       <c r="E25">
-        <v>0.1966822388607987</v>
+        <v>0.3435954128337446</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G25">
-        <v>0.01139970469447018</v>
+        <v>-0.00954937259725345</v>
       </c>
       <c r="H25">
-        <v>0.6</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I25">
-        <v>0.1139970469447018</v>
+        <v>-0.0572962355835207</v>
       </c>
       <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>0.1509895223390005</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>0.3019790446780011</v>
+      </c>
+      <c r="N25">
         <v>3</v>
       </c>
-      <c r="K25">
-        <v>0.08701518803041471</v>
-      </c>
-      <c r="L25">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="M25">
-        <v>0.2610455640912441</v>
-      </c>
-      <c r="N25">
-        <v>8</v>
-      </c>
       <c r="O25">
-        <v>-0.02758236617068222</v>
+        <v>-0.01499356795624696</v>
       </c>
       <c r="P25">
-        <v>0.375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q25">
-        <v>-0.2206589293654577</v>
+        <v>-0.04498070386874087</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B26">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>0.01384058428728717</v>
+        <v>0.03430219321966046</v>
       </c>
       <c r="D26">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="E26">
-        <v>0.2491305171711691</v>
+        <v>0.3430219321966046</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G26">
-        <v>0.00551118566230999</v>
+        <v>-0.00954937259725345</v>
       </c>
       <c r="H26">
-        <v>0.5555555555555556</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I26">
-        <v>0.04960067096078991</v>
+        <v>-0.0572962355835207</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -1761,45 +1749,45 @@
         <v>0.3019790446780011</v>
       </c>
       <c r="N26">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O26">
-        <v>-0.04015962754998226</v>
+        <v>-0.01499356795624696</v>
       </c>
       <c r="P26">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q26">
-        <v>-0.2409577652998935</v>
+        <v>-0.04498070386874087</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B27">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>0.01384058428728717</v>
+        <v>0.03430219321966046</v>
       </c>
       <c r="D27">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="E27">
-        <v>0.2491305171711691</v>
+        <v>0.3430219321966046</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G27">
-        <v>0.00551118566230999</v>
+        <v>-0.00954937259725345</v>
       </c>
       <c r="H27">
-        <v>0.5555555555555556</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I27">
-        <v>0.04960067096078991</v>
+        <v>-0.0572962355835207</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -1814,45 +1802,45 @@
         <v>0.3019790446780011</v>
       </c>
       <c r="N27">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O27">
-        <v>0.002506885934592695</v>
+        <v>-0.01499356795624696</v>
       </c>
       <c r="P27">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q27">
-        <v>0.01504131560755617</v>
+        <v>-0.04498070386874087</v>
       </c>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B28">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C28">
-        <v>0.01400605543426309</v>
+        <v>0.04000611504273247</v>
       </c>
       <c r="D28">
-        <v>0.4444444444444444</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="E28">
-        <v>0.2521089978167357</v>
+        <v>0.3600550353845922</v>
       </c>
       <c r="F28">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>0.008641636954179768</v>
+        <v>0.0133562518537758</v>
       </c>
       <c r="H28">
-        <v>0.5555555555555556</v>
+        <v>0.6</v>
       </c>
       <c r="I28">
-        <v>0.07777473258761791</v>
+        <v>0.06678125926887901</v>
       </c>
       <c r="J28">
         <v>2</v>
@@ -1867,45 +1855,45 @@
         <v>0.3019790446780011</v>
       </c>
       <c r="N28">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O28">
-        <v>0.002506885934592695</v>
+        <v>-0.02416327544005892</v>
       </c>
       <c r="P28">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q28">
-        <v>0.01504131560755617</v>
+        <v>-0.07248982632017675</v>
       </c>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B29">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>0.01400605543426309</v>
+        <v>0.04346602208535107</v>
       </c>
       <c r="D29">
-        <v>0.4444444444444444</v>
+        <v>0.6</v>
       </c>
       <c r="E29">
-        <v>0.2521089978167357</v>
+        <v>0.4346602208535106</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>0.008641636954179768</v>
+        <v>0.0133562518537758</v>
       </c>
       <c r="H29">
-        <v>0.5555555555555556</v>
+        <v>0.6</v>
       </c>
       <c r="I29">
-        <v>0.07777473258761791</v>
+        <v>0.06678125926887901</v>
       </c>
       <c r="J29">
         <v>2</v>
@@ -1920,45 +1908,45 @@
         <v>0.3019790446780011</v>
       </c>
       <c r="N29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O29">
-        <v>0.002506885934592695</v>
+        <v>-0.02416327544005892</v>
       </c>
       <c r="P29">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q29">
-        <v>0.01504131560755617</v>
+        <v>-0.07248982632017675</v>
       </c>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B30">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C30">
-        <v>0.009269765889918229</v>
+        <v>0.04708931656196223</v>
       </c>
       <c r="D30">
-        <v>0.4</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E30">
-        <v>0.1390464883487734</v>
+        <v>0.4238038490576601</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>0.03177965451611842</v>
+        <v>0.009691722121765833</v>
       </c>
       <c r="H30">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="I30">
-        <v>0.1906779270967105</v>
+        <v>0.03876688848706333</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -1973,45 +1961,45 @@
         <v>0.3019790446780011</v>
       </c>
       <c r="N30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O30">
-        <v>-0.001446457984432807</v>
+        <v>-0.02955659480658775</v>
       </c>
       <c r="P30">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>-0.00867874790659684</v>
+        <v>-0.08866978441976325</v>
       </c>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B31">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C31">
-        <v>0.01335322961360574</v>
+        <v>0.04708931656196223</v>
       </c>
       <c r="D31">
-        <v>0.4375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E31">
-        <v>0.2136516738176919</v>
+        <v>0.4238038490576601</v>
       </c>
       <c r="F31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>0.03177965451611842</v>
+        <v>0.009691722121765833</v>
       </c>
       <c r="H31">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="I31">
-        <v>0.1906779270967105</v>
+        <v>0.03876688848706333</v>
       </c>
       <c r="J31">
         <v>2</v>
@@ -2026,45 +2014,45 @@
         <v>0.3019790446780011</v>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O31">
-        <v>-0.001446457984432807</v>
+        <v>-0.02955659480658775</v>
       </c>
       <c r="P31">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>-0.00867874790659684</v>
+        <v>-0.08866978441976325</v>
       </c>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B32">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C32">
-        <v>0.02346824963886383</v>
+        <v>0.04786466831721034</v>
       </c>
       <c r="D32">
-        <v>0.5384615384615384</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="E32">
-        <v>0.3050872453052298</v>
+        <v>0.4307820148548931</v>
       </c>
       <c r="F32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>0.04611175645374669</v>
+        <v>0.009691722121765833</v>
       </c>
       <c r="H32">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="I32">
-        <v>0.2766705387224802</v>
+        <v>0.03876688848706333</v>
       </c>
       <c r="J32">
         <v>2</v>
@@ -2079,45 +2067,45 @@
         <v>0.3019790446780011</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O32">
-        <v>-0.002074181820226784</v>
+        <v>-0.080803339641351</v>
       </c>
       <c r="P32">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>-0.01037090910113392</v>
+        <v>-0.080803339641351</v>
       </c>
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B33">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C33">
-        <v>0.02346824963886383</v>
+        <v>0.04786466831721034</v>
       </c>
       <c r="D33">
-        <v>0.5384615384615384</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="E33">
-        <v>0.3050872453052298</v>
+        <v>0.4307820148548931</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G33">
-        <v>0.04611175645374669</v>
+        <v>0.009691722121765833</v>
       </c>
       <c r="H33">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="I33">
-        <v>0.2766705387224802</v>
+        <v>0.03876688848706333</v>
       </c>
       <c r="J33">
         <v>2</v>
@@ -2132,45 +2120,45 @@
         <v>0.3019790446780011</v>
       </c>
       <c r="N33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O33">
-        <v>-0.002074181820226784</v>
+        <v>-0.080803339641351</v>
       </c>
       <c r="P33">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>-0.01037090910113392</v>
+        <v>-0.080803339641351</v>
       </c>
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B34">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C34">
-        <v>0.01693500467804661</v>
+        <v>0.02488000096302967</v>
       </c>
       <c r="D34">
-        <v>0.5384615384615384</v>
+        <v>0.75</v>
       </c>
       <c r="E34">
-        <v>0.2201550608146059</v>
+        <v>0.1990400077042374</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G34">
-        <v>0.04011697068215891</v>
+        <v>0.01723033279285661</v>
       </c>
       <c r="H34">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I34">
-        <v>0.2005848534107946</v>
+        <v>0.05169099837856983</v>
       </c>
       <c r="J34">
         <v>2</v>
@@ -2185,45 +2173,45 @@
         <v>0.3019790446780011</v>
       </c>
       <c r="N34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O34">
-        <v>-0.0008348214409072222</v>
+        <v>-0.080803339641351</v>
       </c>
       <c r="P34">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>-0.002504464322721667</v>
+        <v>-0.080803339641351</v>
       </c>
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B35">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C35">
-        <v>0.01693500467804661</v>
+        <v>0.04031434373311615</v>
       </c>
       <c r="D35">
-        <v>0.5384615384615384</v>
+        <v>0.75</v>
       </c>
       <c r="E35">
-        <v>0.2201550608146059</v>
+        <v>0.3225147498649292</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G35">
-        <v>0.04011697068215891</v>
+        <v>0.01723033279285661</v>
       </c>
       <c r="H35">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I35">
-        <v>0.2005848534107946</v>
+        <v>0.05169099837856983</v>
       </c>
       <c r="J35">
         <v>2</v>
@@ -2238,652 +2226,1098 @@
         <v>0.3019790446780011</v>
       </c>
       <c r="N35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O35">
-        <v>-0.0008348214409072222</v>
+        <v>-0.080803339641351</v>
       </c>
       <c r="P35">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>-0.002504464322721667</v>
+        <v>-0.080803339641351</v>
       </c>
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C36">
-        <v>0.01376135603730821</v>
+        <v>0.04862633637102309</v>
       </c>
       <c r="D36">
-        <v>0.6</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E36">
-        <v>0.1376135603730821</v>
+        <v>0.3403843545971617</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36">
-        <v>0.05738671207603008</v>
+        <v>0.02910468043572134</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I36">
-        <v>0.2295468483041203</v>
+        <v>0.08731404130716403</v>
       </c>
       <c r="J36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>0.1123308318011945</v>
+        <v>0.1509895223390005</v>
       </c>
       <c r="L36">
         <v>1</v>
       </c>
       <c r="M36">
-        <v>0.3369924954035834</v>
+        <v>0.3019790446780011</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O36">
-        <v>-0.0008348214409072222</v>
+        <v>-0.080803339641351</v>
       </c>
       <c r="P36">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>-0.002504464322721667</v>
+        <v>-0.080803339641351</v>
       </c>
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C37">
-        <v>0.02391710045692026</v>
+        <v>0.04862633637102309</v>
       </c>
       <c r="D37">
-        <v>0.6</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E37">
-        <v>0.2391710045692026</v>
+        <v>0.3403843545971617</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>0.05738671207603008</v>
+        <v>0.02910468043572134</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I37">
-        <v>0.2295468483041203</v>
+        <v>0.08731404130716403</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37">
-        <v>0.1123308318011945</v>
+        <v>0.1509895223390005</v>
       </c>
       <c r="L37">
         <v>1</v>
       </c>
       <c r="M37">
-        <v>0.3369924954035834</v>
+        <v>0.3019790446780011</v>
       </c>
       <c r="N37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O37">
-        <v>-0.0008348214409072222</v>
+        <v>-0.080803339641351</v>
       </c>
       <c r="P37">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>-0.002504464322721667</v>
+        <v>-0.080803339641351</v>
       </c>
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C38">
-        <v>0.02856006770015945</v>
+        <v>0.04862633637102309</v>
       </c>
       <c r="D38">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E38">
-        <v>0.257040609301435</v>
+        <v>0.3403843545971617</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38">
-        <v>0.06911597942518322</v>
+        <v>0.02910468043572134</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I38">
-        <v>0.2764639177007329</v>
+        <v>0.08731404130716403</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38">
-        <v>0.1123308318011945</v>
+        <v>0.1509895223390005</v>
       </c>
       <c r="L38">
         <v>1</v>
       </c>
       <c r="M38">
-        <v>0.3369924954035834</v>
+        <v>0.3019790446780011</v>
       </c>
       <c r="N38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O38">
-        <v>-0.0008348214409072222</v>
+        <v>-0.080803339641351</v>
       </c>
       <c r="P38">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>-0.002504464322721667</v>
+        <v>-0.080803339641351</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="1">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B39">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>0.02856006770015945</v>
+        <v>0.04862633637102309</v>
       </c>
       <c r="D39">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E39">
-        <v>0.257040609301435</v>
+        <v>0.3403843545971617</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>0.06911597942518322</v>
+        <v>0.02910468043572134</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I39">
-        <v>0.2764639177007329</v>
+        <v>0.08731404130716403</v>
       </c>
       <c r="J39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39">
-        <v>0.1123308318011945</v>
+        <v>0.1509895223390005</v>
       </c>
       <c r="L39">
         <v>1</v>
       </c>
       <c r="M39">
-        <v>0.3369924954035834</v>
+        <v>0.3019790446780011</v>
       </c>
       <c r="N39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O39">
-        <v>-0.0008348214409072222</v>
+        <v>-0.080803339641351</v>
       </c>
       <c r="P39">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>-0.002504464322721667</v>
+        <v>-0.080803339641351</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="1">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B40">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>0.02856006770015945</v>
+        <v>0.04862633637102309</v>
       </c>
       <c r="D40">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E40">
-        <v>0.257040609301435</v>
+        <v>0.3403843545971617</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40">
-        <v>0.08009158946036976</v>
+        <v>0.01587399118414412</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I40">
-        <v>0.2402747683811093</v>
+        <v>0.03174798236828824</v>
       </c>
       <c r="J40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K40">
-        <v>0.1123308318011945</v>
+        <v>0.1372461201755328</v>
       </c>
       <c r="L40">
         <v>1</v>
       </c>
       <c r="M40">
-        <v>0.3369924954035834</v>
+        <v>0.2744922403510657</v>
       </c>
       <c r="N40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O40">
-        <v>-0.0008348214409072222</v>
+        <v>-0.080803339641351</v>
       </c>
       <c r="P40">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>-0.002504464322721667</v>
+        <v>-0.080803339641351</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="1">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B41">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>0.02856006770015945</v>
+        <v>0.04862633637102309</v>
       </c>
       <c r="D41">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E41">
-        <v>0.257040609301435</v>
+        <v>0.3403843545971617</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>0.08009158946036976</v>
+        <v>0.01587399118414412</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I41">
-        <v>0.2402747683811093</v>
+        <v>0.03174798236828824</v>
       </c>
       <c r="J41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K41">
-        <v>0.1123308318011945</v>
+        <v>0.1372461201755328</v>
       </c>
       <c r="L41">
         <v>1</v>
       </c>
       <c r="M41">
-        <v>0.3369924954035834</v>
+        <v>0.2744922403510657</v>
       </c>
       <c r="N41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O41">
-        <v>-0.0008348214409072222</v>
+        <v>-0.080803339641351</v>
       </c>
       <c r="P41">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>-0.002504464322721667</v>
+        <v>-0.080803339641351</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="1">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C42">
-        <v>0.02747473923044937</v>
+        <v>0.03098708749092425</v>
       </c>
       <c r="D42">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E42">
-        <v>0.2472726530740443</v>
+        <v>0.2169096124364698</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>0.0759868834739148</v>
+        <v>0.01587399118414412</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I42">
-        <v>0.2279606504217444</v>
+        <v>0.03174798236828824</v>
       </c>
       <c r="J42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K42">
-        <v>0.103168563692216</v>
+        <v>0.1301370797149204</v>
       </c>
       <c r="L42">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M42">
-        <v>0.309505691076648</v>
+        <v>0.2602741594298408</v>
       </c>
       <c r="N42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O42">
-        <v>0.01110329834263668</v>
+        <v>-0.06792218689152385</v>
       </c>
       <c r="P42">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>0.04441319337054672</v>
+        <v>-0.06792218689152385</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="1">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C43">
-        <v>0.02747473923044937</v>
+        <v>0.03098708749092425</v>
       </c>
       <c r="D43">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E43">
-        <v>0.2472726530740443</v>
+        <v>0.2169096124364698</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43">
-        <v>0.0759868834739148</v>
+        <v>0.01587399118414412</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I43">
-        <v>0.2279606504217444</v>
+        <v>0.03174798236828824</v>
       </c>
       <c r="J43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K43">
-        <v>0.103168563692216</v>
+        <v>0.1301370797149204</v>
       </c>
       <c r="L43">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M43">
-        <v>0.309505691076648</v>
+        <v>0.2602741594298408</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O43">
-        <v>0.01110329834263668</v>
+        <v>-0.06792218689152385</v>
       </c>
       <c r="P43">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>0.04441319337054672</v>
+        <v>-0.06792218689152385</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="1">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44">
-        <v>0.01609877608018322</v>
+        <v>0.02778801349987481</v>
       </c>
       <c r="D44">
-        <v>0.6666666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="E44">
-        <v>0.144888984721649</v>
+        <v>0.2223041079989985</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>0.07980201191862631</v>
+        <v>0.01340151001499557</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I44">
-        <v>0.2394060357558789</v>
+        <v>0.02680302002999113</v>
       </c>
       <c r="J44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K44">
-        <v>0.09842920338514105</v>
+        <v>0.2725039737463728</v>
       </c>
       <c r="L44">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="M44">
-        <v>0.2952876101554232</v>
+        <v>0.2725039737463728</v>
       </c>
       <c r="N44">
-        <v>4</v>
-      </c>
-      <c r="O44">
-        <v>0.006873023276335211</v>
-      </c>
-      <c r="P44">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>0.02749209310534084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="1">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45">
-        <v>0.01609877608018322</v>
+        <v>0.02778801349987481</v>
       </c>
       <c r="D45">
-        <v>0.6666666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="E45">
-        <v>0.144888984721649</v>
+        <v>0.2223041079989985</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45">
-        <v>0.07980201191862631</v>
+        <v>0.01340151001499557</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I45">
-        <v>0.2394060357558789</v>
+        <v>0.02680302002999113</v>
       </c>
       <c r="J45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K45">
-        <v>0.09842920338514105</v>
+        <v>0.2725039737463728</v>
       </c>
       <c r="L45">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="M45">
-        <v>0.2952876101554232</v>
+        <v>0.2725039737463728</v>
       </c>
       <c r="N45">
-        <v>4</v>
-      </c>
-      <c r="O45">
-        <v>0.006873023276335211</v>
-      </c>
-      <c r="P45">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>0.02749209310534084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="1">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B46">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C46">
-        <v>0.01750360272491531</v>
+        <v>0.03216054053629935</v>
       </c>
       <c r="D46">
-        <v>0.6666666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="E46">
-        <v>0.1575324245242378</v>
+        <v>0.2572843242903948</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46">
-        <v>0.07339146848602922</v>
+        <v>0.01340151001499557</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I46">
-        <v>0.2201744054580876</v>
+        <v>0.02680302002999113</v>
       </c>
       <c r="J46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K46">
-        <v>0.0988133362823967</v>
+        <v>0.2725039737463728</v>
       </c>
       <c r="L46">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="M46">
-        <v>0.2964400088471901</v>
+        <v>0.2725039737463728</v>
       </c>
       <c r="N46">
-        <v>2</v>
-      </c>
-      <c r="O46">
-        <v>0.1366167398336149</v>
-      </c>
-      <c r="P46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>0.2732334796672298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B47">
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <v>0.03216054053629935</v>
+      </c>
+      <c r="D47">
+        <v>0.875</v>
+      </c>
+      <c r="E47">
+        <v>0.2572843242903948</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+      <c r="G47">
+        <v>0.01340151001499557</v>
+      </c>
+      <c r="H47">
+        <v>0.5</v>
+      </c>
+      <c r="I47">
+        <v>0.02680302002999113</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48" s="1">
+        <v>51</v>
+      </c>
+      <c r="B48">
+        <v>8</v>
+      </c>
+      <c r="C48">
+        <v>0.03200247977100557</v>
+      </c>
+      <c r="D48">
+        <v>0.875</v>
+      </c>
+      <c r="E48">
+        <v>0.2560198381680445</v>
+      </c>
+      <c r="F48">
+        <v>2</v>
+      </c>
+      <c r="G48">
+        <v>0.01340151001499557</v>
+      </c>
+      <c r="H48">
+        <v>0.5</v>
+      </c>
+      <c r="I48">
+        <v>0.02680302002999113</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" s="1">
+        <v>52</v>
+      </c>
+      <c r="B49">
+        <v>8</v>
+      </c>
+      <c r="C49">
+        <v>0.03200247977100557</v>
+      </c>
+      <c r="D49">
+        <v>0.875</v>
+      </c>
+      <c r="E49">
+        <v>0.2560198381680445</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="G49">
+        <v>0.01340151001499557</v>
+      </c>
+      <c r="H49">
+        <v>0.5</v>
+      </c>
+      <c r="I49">
+        <v>0.02680302002999113</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17">
+      <c r="A50" s="1">
+        <v>53</v>
+      </c>
+      <c r="B50">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>0.03053013924699588</v>
+      </c>
+      <c r="D50">
+        <v>0.875</v>
+      </c>
+      <c r="E50">
+        <v>0.244241113975967</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>-0.01847615672850189</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>-0.01847615672850189</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="L50">
+        <v>1</v>
+      </c>
+      <c r="M50">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17">
+      <c r="A51" s="1">
+        <v>54</v>
+      </c>
+      <c r="B51">
+        <v>8</v>
+      </c>
+      <c r="C51">
+        <v>0.03053013924699588</v>
+      </c>
+      <c r="D51">
+        <v>0.875</v>
+      </c>
+      <c r="E51">
+        <v>0.244241113975967</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>-0.01847615672850189</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>-0.01847615672850189</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="A52" s="1">
+        <v>55</v>
+      </c>
+      <c r="B52">
         <v>9</v>
       </c>
-      <c r="C47">
-        <v>0.01750360272491531</v>
-      </c>
-      <c r="D47">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E47">
-        <v>0.1575324245242378</v>
-      </c>
-      <c r="F47">
-        <v>3</v>
-      </c>
-      <c r="G47">
-        <v>0.07339146848602922</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47">
-        <v>0.2201744054580876</v>
-      </c>
-      <c r="J47">
-        <v>3</v>
-      </c>
-      <c r="K47">
-        <v>0.0988133362823967</v>
-      </c>
-      <c r="L47">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="M47">
-        <v>0.2964400088471901</v>
-      </c>
-      <c r="N47">
-        <v>2</v>
-      </c>
-      <c r="O47">
-        <v>0.1366167398336149</v>
-      </c>
-      <c r="P47">
-        <v>1</v>
-      </c>
-      <c r="Q47">
-        <v>0.2732334796672298</v>
+      <c r="C52">
+        <v>0.01626750321686653</v>
+      </c>
+      <c r="D52">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="E52">
+        <v>0.1464075289517988</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52">
+        <v>-0.08504586185490348</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>-0.170091723709807</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17">
+      <c r="A53" s="1">
+        <v>56</v>
+      </c>
+      <c r="B53">
+        <v>9</v>
+      </c>
+      <c r="C53">
+        <v>0.01626750321686653</v>
+      </c>
+      <c r="D53">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="E53">
+        <v>0.1464075289517988</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
+      </c>
+      <c r="G53">
+        <v>-0.08504586185490348</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>-0.170091723709807</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <v>0.2725039737463728</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17">
+      <c r="A54" s="1">
+        <v>57</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+      <c r="C54">
+        <v>0.005002048920844437</v>
+      </c>
+      <c r="D54">
+        <v>0.75</v>
+      </c>
+      <c r="E54">
+        <v>0.0400163913667555</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <v>-0.1229906578358753</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>-0.2459813156717505</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>0.264392340600784</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54">
+        <v>0.264392340600784</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17">
+      <c r="A55" s="1">
+        <v>58</v>
+      </c>
+      <c r="B55">
+        <v>8</v>
+      </c>
+      <c r="C55">
+        <v>0.005002048920844437</v>
+      </c>
+      <c r="D55">
+        <v>0.75</v>
+      </c>
+      <c r="E55">
+        <v>0.0400163913667555</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+      <c r="G55">
+        <v>-0.1229906578358753</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>-0.2459813156717505</v>
+      </c>
+      <c r="J55">
+        <v>2</v>
+      </c>
+      <c r="K55">
+        <v>0.120314758339565</v>
+      </c>
+      <c r="L55">
+        <v>0.5</v>
+      </c>
+      <c r="M55">
+        <v>0.2406295166791299</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17">
+      <c r="A56" s="1">
+        <v>59</v>
+      </c>
+      <c r="B56">
+        <v>8</v>
+      </c>
+      <c r="C56">
+        <v>0.006355798014846314</v>
+      </c>
+      <c r="D56">
+        <v>0.75</v>
+      </c>
+      <c r="E56">
+        <v>0.05084638411877052</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="G56">
+        <v>-0.1229906578358753</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>-0.2459813156717505</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <v>-0.02376282392165407</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>-0.02376282392165407</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17">
+      <c r="A57" s="1">
+        <v>60</v>
+      </c>
+      <c r="B57">
+        <v>8</v>
+      </c>
+      <c r="C57">
+        <v>0.006355798014846314</v>
+      </c>
+      <c r="D57">
+        <v>0.75</v>
+      </c>
+      <c r="E57">
+        <v>0.05084638411877052</v>
+      </c>
+      <c r="F57">
+        <v>2</v>
+      </c>
+      <c r="G57">
+        <v>-0.1229906578358753</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>-0.2459813156717505</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57">
+        <v>-0.02376282392165407</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>-0.02376282392165407</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
